--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_05/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_05/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>52.33</v>
+        <v>54.81</v>
       </c>
       <c r="D2" t="n">
-        <v>23.09</v>
+        <v>22.67</v>
       </c>
       <c r="E2" t="n">
-        <v>44.12</v>
+        <v>41.35</v>
       </c>
       <c r="F2" t="n">
-        <v>28.61</v>
+        <v>30.12</v>
       </c>
       <c r="G2" t="n">
-        <v>33.22</v>
+        <v>35.48</v>
       </c>
       <c r="H2" t="n">
-        <v>42.59</v>
+        <v>46.24</v>
       </c>
       <c r="I2" t="n">
-        <v>70.70999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>71.39</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>33.64</v>
+        <v>38.74</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>2.41</v>
+        <v>1.02</v>
       </c>
       <c r="F3" t="n">
-        <v>30.75</v>
+        <v>38.57</v>
       </c>
       <c r="G3" t="n">
-        <v>33.67</v>
+        <v>38.58</v>
       </c>
       <c r="H3" t="n">
-        <v>33.67</v>
+        <v>38.59</v>
       </c>
       <c r="I3" t="n">
-        <v>33.71</v>
+        <v>38.61</v>
       </c>
       <c r="J3" t="n">
-        <v>35.92</v>
+        <v>40.54</v>
       </c>
       <c r="K3" t="n">
-        <v>5.17</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>6.23</v>
+        <v>6.94</v>
       </c>
       <c r="D4" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="E4" t="n">
-        <v>24.79</v>
+        <v>21.52</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.13</v>
+        <v>5.55</v>
       </c>
       <c r="H4" t="n">
-        <v>5.49</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.67</v>
+        <v>7.52</v>
       </c>
       <c r="J4" t="n">
-        <v>9.9</v>
+        <v>10.09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>83.75</v>
+        <v>85.34</v>
       </c>
       <c r="D5" t="n">
-        <v>33.69</v>
+        <v>18.69</v>
       </c>
       <c r="E5" t="n">
-        <v>40.23</v>
+        <v>21.91</v>
       </c>
       <c r="F5" t="n">
-        <v>60.21</v>
+        <v>62.24</v>
       </c>
       <c r="G5" t="n">
-        <v>64.33</v>
+        <v>72.8</v>
       </c>
       <c r="H5" t="n">
-        <v>66.39</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>74.06</v>
+        <v>98.64</v>
       </c>
       <c r="J5" t="n">
-        <v>157.06</v>
+        <v>139.73</v>
       </c>
       <c r="K5" t="n">
-        <v>96.84999999999999</v>
+        <v>77.48999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.07</v>
+        <v>4.18</v>
       </c>
       <c r="D6" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>19.36</v>
+        <v>11.88</v>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>3.51</v>
       </c>
       <c r="G6" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.95</v>
+        <v>4.02</v>
       </c>
       <c r="I6" t="n">
-        <v>3.21</v>
+        <v>4.82</v>
       </c>
       <c r="J6" t="n">
-        <v>4.76</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>
